--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soMultiChannel.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soMultiChannel.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>卖家订单编号</t>
   </si>
@@ -107,6 +107,9 @@
     <t>异常信息</t>
   </si>
   <si>
+    <t>系统已出库</t>
+  </si>
+  <si>
     <t>{.deliveryCode}</t>
   </si>
   <si>
@@ -183,6 +186,9 @@
   </si>
   <si>
     <t>{.signOrderError}</t>
+  </si>
+  <si>
+    <t>{.outstockStatusName}</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1381,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -1391,10 +1397,10 @@
     <col min="20" max="20" width="11.125" customWidth="1"/>
     <col min="21" max="21" width="12.375" customWidth="1"/>
     <col min="22" max="22" width="11.75" customWidth="1"/>
-    <col min="26" max="26" width="12.875" customWidth="1"/>
+    <col min="26" max="27" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:26">
+    <row r="1" ht="30" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1473,85 +1479,91 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soMultiChannel.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soMultiChannel.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="采购调价数据" sheetId="1" r:id="rId1"/>
+    <sheet name="多渠道订单" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
